--- a/jogos_2025-01-02.xlsx
+++ b/jogos_2025-01-02.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,43 +669,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="M2" t="n">
         <v>2.63</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
         <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="S2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X2" t="n">
         <v>2.1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.2</v>
       </c>
       <c r="Y2" t="n">
         <v>3</v>
@@ -714,38 +714,38 @@
         <v>1.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['18', '28', '59']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['44', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45659.35416666666</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,43 +927,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M4" t="n">
         <v>2.63</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
         <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R4" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="X4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Y4" t="n">
         <v>3</v>
@@ -972,38 +972,38 @@
         <v>1.36</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['18', '28', '59']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44', '59']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45659.35416666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>2.82</v>
       </c>
       <c r="M8" t="n">
-        <v>3.73</v>
+        <v>3.26</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3</v>
+        <v>2.17</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['7', '66', '81']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['45+11']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['24', '60']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45659.5</v>
@@ -1546,19 +1546,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1572,34 +1572,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.86</v>
+        <v>3.34</v>
       </c>
       <c r="M9" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="N9" t="n">
-        <v>3.68</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
         <v>1.05</v>
@@ -1608,7 +1608,7 @@
         <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="Y9" t="n">
         <v>1.92</v>
@@ -1617,38 +1617,38 @@
         <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['45+4']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.21</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.98</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45659.5</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1701,34 +1701,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.34</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>3.68</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
         <v>1.05</v>
@@ -1737,7 +1737,7 @@
         <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="Y10" t="n">
         <v>1.92</v>
@@ -1746,38 +1746,38 @@
         <v>1.9</v>
       </c>
       <c r="AA10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['45+4']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45659.5</v>
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.82</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>3.26</v>
+        <v>3.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>3.03</v>
       </c>
       <c r="O11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
         <v>3.25</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['8', '65']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['7', '66', '81']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45659.5</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.13</v>
+        <v>3.73</v>
       </c>
       <c r="N12" t="n">
-        <v>3.03</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
         <v>2.5</v>
@@ -1989,7 +1989,7 @@
         <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
         <v>1.22</v>
@@ -1998,44 +1998,44 @@
         <v>4.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB12" t="n">
         <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['8', '65']</t>
+          <t>['45+11']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '60']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45659.5</v>
@@ -2320,109 +2320,109 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['49', '77']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['7', '26', '76']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45659.69791666666</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.06</v>
+        <v>2.38</v>
       </c>
       <c r="M16" t="n">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="N16" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['7', '26', '76']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['90+2']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['49', '77']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45659.69791666666</v>
